--- a/data/Data anual 1935 2025 Ferreres.xlsx
+++ b/data/Data anual 1935 2025 Ferreres.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EAB9A91-7634-7C43-B5AD-D4DD3A81C1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81D394B-C299-9049-8C20-F9A2025347F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="2820" windowWidth="26440" windowHeight="15440" xr2:uid="{1B7A2EE2-BD14-2944-88AB-F9FB21A0117E}"/>
+    <workbookView xWindow="2700" yWindow="2500" windowWidth="26440" windowHeight="15440" xr2:uid="{1B7A2EE2-BD14-2944-88AB-F9FB21A0117E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Año</t>
-  </si>
-  <si>
     <t>PBIpm</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t>Ptrigo_USA</t>
+  </si>
+  <si>
+    <t>año</t>
   </si>
 </sst>
 </file>
@@ -536,25 +536,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">

--- a/data/Data anual 1935 2025 Ferreres.xlsx
+++ b/data/Data anual 1935 2025 Ferreres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81D394B-C299-9049-8C20-F9A2025347F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDC9F34-4E27-C842-9A7D-532DCCE8797A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2700" yWindow="2500" windowWidth="26440" windowHeight="15440" xr2:uid="{1B7A2EE2-BD14-2944-88AB-F9FB21A0117E}"/>
   </bookViews>
@@ -47,9 +47,6 @@
     <t>ipc</t>
   </si>
   <si>
-    <t xml:space="preserve">E </t>
-  </si>
-  <si>
     <t>Psoja_USA</t>
   </si>
   <si>
@@ -60,6 +57,9 @@
   </si>
   <si>
     <t>año</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -536,7 +536,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -545,16 +545,16 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
-      </c>
-      <c r="G1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">

--- a/data/Data anual 1935 2025 Ferreres.xlsx
+++ b/data/Data anual 1935 2025 Ferreres.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariana/Library/CloudStorage/GoogleDrive-marianabarrenadrive@gmail.com/Mi unidad/TESIS UCA/UCA Proyecto de TESIS/Estadísticas/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEDC9F34-4E27-C842-9A7D-532DCCE8797A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA23F5E6-F954-6B4A-90AA-0A617CB8734D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2700" yWindow="2500" windowWidth="26440" windowHeight="15440" xr2:uid="{1B7A2EE2-BD14-2944-88AB-F9FB21A0117E}"/>
+    <workbookView xWindow="-4560" yWindow="-21600" windowWidth="38400" windowHeight="21600" xr2:uid="{1B7A2EE2-BD14-2944-88AB-F9FB21A0117E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>PBIpm</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>impp_usa</t>
   </si>
 </sst>
 </file>
@@ -528,13 +531,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B42373A-3AB1-B041-A33C-389EBB7B03A1}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="4" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -556,8 +559,11 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1935</v>
       </c>
@@ -579,8 +585,11 @@
       <c r="G2" s="4">
         <v>0.85958333333333325</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H2">
+        <v>4.4057394210779064</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1936</v>
       </c>
@@ -602,8 +611,11 @@
       <c r="G3" s="4">
         <v>0.95783333333333343</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H3">
+        <v>4.7204350940120428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1937</v>
       </c>
@@ -625,8 +637,11 @@
       <c r="G4" s="4">
         <v>1.0713333333333332</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H4">
+        <v>5.2762612176359704</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1938</v>
       </c>
@@ -648,8 +663,11 @@
       <c r="G5" s="4">
         <v>0.66116666666666657</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H5">
+        <v>4.7653916187169196</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1939</v>
       </c>
@@ -671,8 +689,11 @@
       <c r="G6" s="4">
         <v>0.63558333333333328</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H6">
+        <v>4.8266959705872052</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1940</v>
       </c>
@@ -694,8 +715,11 @@
       <c r="G7" s="4">
         <v>0.73908333333333343</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H7">
+        <v>5.165913384269456</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1941</v>
       </c>
@@ -717,8 +741,11 @@
       <c r="G8" s="4">
         <v>0.8394999999999998</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H8">
+        <v>5.5092177547430596</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1942</v>
       </c>
@@ -740,8 +767,11 @@
       <c r="G9" s="4">
         <v>1.0185</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H9">
+        <v>6.4410439031714102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1943</v>
       </c>
@@ -763,8 +793,11 @@
       <c r="G10" s="4">
         <v>1.2733333333333334</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H10">
+        <v>6.9723482860472243</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1944</v>
       </c>
@@ -786,8 +819,11 @@
       <c r="G11" s="4">
         <v>1.4283333333333335</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H11">
+        <v>7.434174403470049</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1945</v>
       </c>
@@ -809,8 +845,11 @@
       <c r="G12" s="4">
         <v>1.4858333333333331</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H12">
+        <v>7.6630439837857836</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1946</v>
       </c>
@@ -832,8 +871,11 @@
       <c r="G13" s="4">
         <v>1.7358333333333331</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H13">
+        <v>8.5008701260130284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1947</v>
       </c>
@@ -855,8 +897,11 @@
       <c r="G14" s="4">
         <v>2.34</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H14">
+        <v>10.393131120409201</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1948</v>
       </c>
@@ -878,8 +923,11 @@
       <c r="G15" s="4">
         <v>2.1491666666666664</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H15">
+        <v>11.537479021987874</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1949</v>
       </c>
@@ -901,8 +949,11 @@
       <c r="G16" s="4">
         <v>1.9166666666666667</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16">
+        <v>10.977565941572596</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1950</v>
       </c>
@@ -924,8 +975,11 @@
       <c r="G17" s="4">
         <v>1.9808333333333334</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17">
+        <v>11.880783392461481</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1951</v>
       </c>
@@ -947,8 +1001,11 @@
       <c r="G18" s="4">
         <v>2.1191666666666666</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18">
+        <v>14.94600098597579</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1952</v>
       </c>
@@ -970,8 +1027,11 @@
       <c r="G19" s="4">
         <v>2.1150000000000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19">
+        <v>14.149044411662073</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1953</v>
       </c>
@@ -993,8 +1053,11 @@
       <c r="G20" s="4">
         <v>1.9891666666666667</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20">
+        <v>13.568696547290031</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1954</v>
       </c>
@@ -1016,8 +1079,11 @@
       <c r="G21" s="4">
         <v>2.0475000000000003</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>13.850696565893344</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1955</v>
       </c>
@@ -1039,8 +1105,11 @@
       <c r="G22" s="4">
         <v>2.0241666666666664</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>13.813913954771177</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1956</v>
       </c>
@@ -1062,8 +1131,11 @@
       <c r="G23" s="4">
         <v>1.9758333333333333</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>14.128609627705313</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1957</v>
       </c>
@@ -1085,8 +1157,11 @@
       <c r="G24" s="4">
         <v>1.9724999999999999</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24">
+        <v>14.212204605588674</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1958</v>
       </c>
@@ -1108,8 +1183,11 @@
       <c r="G25" s="4">
         <v>1.7933333333333332</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25">
+        <v>13.560490712012449</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1959</v>
       </c>
@@ -1131,8 +1209,11 @@
       <c r="G26" s="4">
         <v>1.7458333333333333</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26">
+        <v>13.311061996808199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1960</v>
       </c>
@@ -1154,8 +1235,11 @@
       <c r="G27" s="4">
         <v>1.7608333333333335</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27">
+        <v>13.483202941044725</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1961</v>
       </c>
@@ -1177,8 +1261,11 @@
       <c r="G28" s="4">
         <v>1.8083333333333331</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28">
+        <v>13.30052275528705</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1962</v>
       </c>
@@ -1200,8 +1287,11 @@
       <c r="G29" s="4">
         <v>1.9583333333333333</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29">
+        <v>13.015963235199624</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1963</v>
       </c>
@@ -1223,8 +1313,11 @@
       <c r="G30" s="4">
         <v>1.9400000000000002</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30">
+        <v>13.096764086592451</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1964</v>
       </c>
@@ -1246,8 +1339,11 @@
       <c r="G31" s="4">
         <v>1.6016666666666666</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31">
+        <v>13.490229101965125</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1965</v>
       </c>
@@ -1269,8 +1365,11 @@
       <c r="G32" s="4">
         <v>1.3475000000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32">
+        <v>13.56400379243755</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1966</v>
       </c>
@@ -1292,8 +1391,11 @@
       <c r="G33" s="4">
         <v>1.551666666666667</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33">
+        <v>13.929364163988051</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1967</v>
       </c>
@@ -1315,8 +1417,11 @@
       <c r="G34" s="4">
         <v>1.4708333333333332</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34">
+        <v>14.052321981324926</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1968</v>
       </c>
@@ -1338,8 +1443,11 @@
       <c r="G35" s="4">
         <v>1.3008333333333333</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35">
+        <v>14.213923684145724</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1969</v>
       </c>
@@ -1361,8 +1469,11 @@
       <c r="G36" s="4">
         <v>1.2549999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36">
+        <v>14.629940020623625</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1970</v>
       </c>
@@ -1384,8 +1495,11 @@
       <c r="G37" s="4">
         <v>1.3308333333333333</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37">
+        <v>15.630009007273875</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1971</v>
       </c>
@@ -1407,8 +1521,11 @@
       <c r="G38" s="4">
         <v>1.3599999999999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38">
+        <v>16.438240861454727</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1972</v>
       </c>
@@ -1430,8 +1547,11 @@
       <c r="G39" s="4">
         <v>1.5733333333333335</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39">
+        <v>17.633291851947924</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1973</v>
       </c>
@@ -1453,8 +1573,11 @@
       <c r="G40" s="4">
         <v>3.1566666666666663</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40">
+        <v>20.954275657195375</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>1974</v>
       </c>
@@ -1476,8 +1599,11 @@
       <c r="G41" s="4">
         <v>4.4841666666666669</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41">
+        <v>31.033587300993851</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1975</v>
       </c>
@@ -1499,8 +1625,11 @@
       <c r="G42" s="4">
         <v>3.6775000000000002</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42">
+        <v>33.826232773745524</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>1976</v>
       </c>
@@ -1522,8 +1651,11 @@
       <c r="G43" s="4">
         <v>3.1458333333333335</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43">
+        <v>34.860895341889076</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1977</v>
       </c>
@@ -1545,8 +1677,11 @@
       <c r="G44" s="4">
         <v>2.29</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44">
+        <v>37.634671588317353</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>1978</v>
       </c>
@@ -1568,8 +1703,11 @@
       <c r="G45" s="4">
         <v>2.8241666666666663</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45">
+        <v>40.917916941169523</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1979</v>
       </c>
@@ -1591,8 +1729,11 @@
       <c r="G46" s="4">
         <v>3.5091666666666668</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46">
+        <v>47.993876753423578</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1980</v>
       </c>
@@ -1614,8 +1755,11 @@
       <c r="G47" s="4">
         <v>3.8825000000000003</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47">
+        <v>61.133147907170674</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1981</v>
       </c>
@@ -1637,8 +1781,11 @@
       <c r="G48" s="4">
         <v>3.875</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48">
+        <v>64.403813775912027</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1982</v>
       </c>
@@ -1660,8 +1807,11 @@
       <c r="G49" s="4">
         <v>3.5216666666666665</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49">
+        <v>63.108126912532697</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1983</v>
       </c>
@@ -1683,8 +1833,11 @@
       <c r="G50" s="4">
         <v>3.5833333333333335</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50">
+        <v>60.77148773908003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1984</v>
       </c>
@@ -1706,8 +1859,11 @@
       <c r="G51" s="4">
         <v>3.4624999999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51">
+        <v>61.815584920180775</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>1985</v>
       </c>
@@ -1729,8 +1885,11 @@
       <c r="G52" s="4">
         <v>3.1966666666666668</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52">
+        <v>60.296612213834919</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>1986</v>
       </c>
@@ -1752,8 +1911,11 @@
       <c r="G53" s="4">
         <v>2.7074999999999996</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53">
+        <v>58.324778079595077</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>1987</v>
       </c>
@@ -1775,8 +1937,11 @@
       <c r="G54" s="4">
         <v>2.5525000000000002</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54">
+        <v>62.318764284832326</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1988</v>
       </c>
@@ -1798,8 +1963,11 @@
       <c r="G55" s="4">
         <v>3.3266666666666667</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55">
+        <v>65.764108869962186</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1989</v>
       </c>
@@ -1821,8 +1989,11 @@
       <c r="G56" s="4">
         <v>3.8758333333333335</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56">
+        <v>71.82016813835736</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1990</v>
       </c>
@@ -1844,8 +2015,11 @@
       <c r="G57" s="4">
         <v>2.9808333333333334</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57">
+        <v>74.146165068363501</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1991</v>
       </c>
@@ -1867,8 +2041,11 @@
       <c r="G58" s="4">
         <v>2.7383333333333333</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58">
+        <v>74.196294312544651</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1992</v>
       </c>
@@ -1890,8 +2067,11 @@
       <c r="G59" s="4">
         <v>3.3824999999999998</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59">
+        <v>74.807755504436315</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1993</v>
       </c>
@@ -1913,8 +2093,11 @@
       <c r="G60" s="4">
         <v>3.2058333333333335</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60">
+        <v>74.636871508379798</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>1994</v>
       </c>
@@ -1936,8 +2119,11 @@
       <c r="G61" s="4">
         <v>3.5158333333333331</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61">
+        <v>75.892211633256579</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>1995</v>
       </c>
@@ -1959,8 +2145,11 @@
       <c r="G62" s="4">
         <v>4.0925000000000002</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62">
+        <v>79.316464015773832</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>1996</v>
       </c>
@@ -1982,8 +2171,11 @@
       <c r="G63" s="4">
         <v>4.7666666666666666</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63">
+        <v>80.118304304962095</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>1997</v>
       </c>
@@ -2005,8 +2197,11 @@
       <c r="G64" s="4">
         <v>3.7124999999999999</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64">
+        <v>78.146565888925323</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>1998</v>
       </c>
@@ -2028,8 +2223,11 @@
       <c r="G65" s="4">
         <v>2.9033333333333333</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H65">
+        <v>73.434111074597411</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1999</v>
       </c>
@@ -2051,8 +2249,11 @@
       <c r="G66" s="4">
         <v>2.5758333333333336</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H66">
+        <v>74.065067367729142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2000</v>
       </c>
@@ -2074,8 +2275,11 @@
       <c r="G67" s="4">
         <v>2.5683333333333334</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H67">
+        <v>78.869536641472166</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>2001</v>
       </c>
@@ -2097,8 +2301,11 @@
       <c r="G68" s="4">
         <v>2.8299999999999996</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H68">
+        <v>76.07624055208673</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>2002</v>
       </c>
@@ -2120,8 +2327,11 @@
       <c r="G69" s="4">
         <v>3.4058333333333337</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H69">
+        <v>74.196516595464928</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>2003</v>
       </c>
@@ -2143,8 +2353,11 @@
       <c r="G70" s="4">
         <v>3.4449999999999998</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H70">
+        <v>76.385146237265829</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>2004</v>
       </c>
@@ -2166,8 +2379,11 @@
       <c r="G71" s="4">
         <v>3.5683333333333334</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H71">
+        <v>80.69010844561285</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>2005</v>
       </c>
@@ -2189,8 +2405,11 @@
       <c r="G72" s="4">
         <v>3.3591666666666673</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H72">
+        <v>86.749917844232627</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>2006</v>
       </c>
@@ -2212,8 +2431,11 @@
       <c r="G73" s="4">
         <v>4.0333333333333332</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H73">
+        <v>90.976010515938171</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>2007</v>
       </c>
@@ -2235,8 +2457,11 @@
       <c r="G74" s="4">
         <v>5.7591666666666663</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H74">
+        <v>94.814327965823168</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>2008</v>
       </c>
@@ -2258,8 +2483,11 @@
       <c r="G75" s="4">
         <v>8.019166666666667</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H75">
+        <v>105.72461386789327</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>2009</v>
       </c>
@@ -2281,8 +2509,11 @@
       <c r="G76" s="4">
         <v>5.3041666666666663</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H76">
+        <v>93.572132763719978</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>2010</v>
       </c>
@@ -2304,8 +2535,11 @@
       <c r="G77" s="4">
         <v>5.1150000000000002</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H77">
+        <v>100.00000000000009</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>2011</v>
       </c>
@@ -2327,8 +2561,11 @@
       <c r="G78" s="4">
         <v>7.4366666666666674</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H78">
+        <v>110.90371344068376</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>2012</v>
       </c>
@@ -2350,8 +2587,11 @@
       <c r="G79" s="4">
         <v>7.5983333333333327</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H79">
+        <v>111.21261912586274</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>2013</v>
       </c>
@@ -2373,8 +2613,11 @@
       <c r="G80" s="4">
         <v>7.315833333333333</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H80">
+        <v>109.99014130791974</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>2014</v>
       </c>
@@ -2396,8 +2639,11 @@
       <c r="G81" s="4">
         <v>6.3333333333333339</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H81">
+        <v>108.807098258298</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>2015</v>
       </c>
@@ -2419,8 +2665,11 @@
       <c r="G82" s="4">
         <v>5.2758333333333338</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H82">
+        <v>97.739073282944503</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>2016</v>
       </c>
@@ -2442,8 +2691,11 @@
       <c r="G83" s="4">
         <v>4.1091666666666669</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H83">
+        <v>94.485704896483796</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>2017</v>
       </c>
@@ -2465,8 +2717,11 @@
       <c r="G84" s="4">
         <v>4.4366666666666674</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H84">
+        <v>97.226421294774923</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>2018</v>
       </c>
@@ -2488,8 +2743,11 @@
       <c r="G85" s="4">
         <v>5.1433333333333326</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H85">
+        <v>100.26947091685859</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>2019</v>
       </c>
@@ -2511,8 +2769,11 @@
       <c r="G86" s="4">
         <v>4.7433333333333332</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H86">
+        <v>98.994413407821256</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>2020</v>
       </c>
@@ -2534,8 +2795,11 @@
       <c r="G87" s="4">
         <v>4.8574999999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H87">
+        <v>96.523167926388467</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>2021</v>
       </c>
@@ -2557,8 +2821,11 @@
       <c r="G88" s="4">
         <v>6.84</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H88">
+        <v>105.060795267828</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>2022</v>
       </c>
@@ -2580,8 +2847,11 @@
       <c r="G89" s="4">
         <v>9.3000000000000007</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H89">
+        <v>113.95333552415376</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>2023</v>
       </c>
@@ -2603,8 +2873,11 @@
       <c r="G90" s="4">
         <v>7.6691666666666674</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H90">
+        <v>110.43049622083474</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>2024</v>
       </c>
@@ -2627,7 +2900,7 @@
         <v>5.7991666666666672</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>2025</v>
       </c>
